--- a/英语群_20260816.xlsx
+++ b/英语群_20260816.xlsx
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C1" s="24">
         <f>SUM(C3:C1001)</f>
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D1" s="24">
         <f>SUM(D3:D1001)</f>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E1" s="24">
         <f>SUM(E3:E1001)</f>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>0</v>
@@ -1326,21 +1326,21 @@
       </c>
       <c r="C3" s="3">
         <f t="shared" ref="C3:C52" si="1">F3+J3</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3">
         <f t="shared" ref="D3:D52" si="2">G3+K3</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="3">
         <f t="shared" ref="E3:E52" si="3">H3+L3</f>
         <v>6</v>
       </c>
       <c r="F3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -1834,20 +1834,20 @@
       </c>
       <c r="D15" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" s="5">
         <v>0</v>
       </c>
       <c r="G15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="25">
         <v>15</v>
@@ -2418,21 +2418,21 @@
       </c>
       <c r="C29" s="3">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" s="3">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="F29" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="5">
         <v>0</v>
@@ -2712,21 +2712,21 @@
       </c>
       <c r="C36" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="3">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="F36" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="5">
         <v>0</v>
@@ -2796,21 +2796,21 @@
       </c>
       <c r="C38" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" s="3">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="5">
         <v>0</v>
@@ -3006,21 +3006,21 @@
       </c>
       <c r="C43" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="3">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="F43" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="5">
         <v>0</v>
